--- a/XD_JIG/XD12/XD12_PWM_Rev_1/측정자료/xd12_pwm_osc_250407.xlsx
+++ b/XD_JIG/XD12/XD12_PWM_Rev_1/측정자료/xd12_pwm_osc_250407.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12_PWM_Rev_1\측정자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81D68AE-E6CD-4430-B02C-8C23EB9194E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93578195-63FF-4604-AFA1-DF9B96103FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
